--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1456F3F-47D8-4E1A-8875-7E191CC40679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F372A5D2-D243-4AF4-A26D-5BD8960C6071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
   <si>
     <t>type</t>
   </si>
@@ -391,6 +391,15 @@
   </si>
   <si>
     <t>205(109786)</t>
+  </si>
+  <si>
+    <t>Effective and enduring place-based interventions against firearm violence and serious crime require mechanism-based analytical thinking</t>
+  </si>
+  <si>
+    <t>American Journal of Public Health</t>
+  </si>
+  <si>
+    <t>(Forthcoming)</t>
   </si>
 </sst>
 </file>
@@ -763,17 +772,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="36.81640625" customWidth="1"/>
-    <col min="4" max="4" width="65.26953125" customWidth="1"/>
-    <col min="5" max="5" width="34.453125" customWidth="1"/>
-    <col min="6" max="6" width="42.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="36.7890625" customWidth="1"/>
+    <col min="4" max="4" width="65.26171875" customWidth="1"/>
+    <col min="5" max="5" width="34.47265625" customWidth="1"/>
+    <col min="6" max="6" width="42.47265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -825,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -851,7 +860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -877,7 +886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -903,7 +912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -929,7 +938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -955,7 +964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -972,7 +981,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -989,7 +998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1006,7 +1015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1023,7 +1032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1043,7 +1052,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1066,7 +1075,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1092,7 +1101,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1118,7 +1127,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1141,7 +1150,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1158,7 +1167,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1193,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1210,7 +1219,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1233,7 +1242,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1259,7 +1268,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1282,7 +1291,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1308,7 +1317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1334,7 +1343,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1358,6 +1367,23 @@
       </c>
       <c r="H25" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F372A5D2-D243-4AF4-A26D-5BD8960C6071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACAFB8E-14C7-4FE2-BD1C-AC3CD9F4041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>type</t>
   </si>
@@ -399,7 +399,10 @@
     <t>American Journal of Public Health</t>
   </si>
   <si>
-    <t>(Forthcoming)</t>
+    <t>10.2105/AJPH.2026.308569</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2105/AJPH.2026.308569</t>
   </si>
 </sst>
 </file>
@@ -1376,14 +1379,20 @@
       <c r="B26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
-        <v>124</v>
+      <c r="C26">
+        <v>2026</v>
       </c>
       <c r="D26" t="s">
         <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>123</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1402,8 +1411,9 @@
     <hyperlink ref="F23" r:id="rId12" xr:uid="{414F80D1-F804-4ABF-AFEB-433C82EECD71}"/>
     <hyperlink ref="F24" r:id="rId13" xr:uid="{AF656063-5565-482A-8E9F-6EF001DB19F8}"/>
     <hyperlink ref="F25" r:id="rId14" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
+    <hyperlink ref="F26" r:id="rId15" xr:uid="{8821F420-E4C6-420E-A3D3-50FB15810E34}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACAFB8E-14C7-4FE2-BD1C-AC3CD9F4041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BACAFB8E-14C7-4FE2-BD1C-AC3CD9F4041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D011DA-42D9-4FD3-9173-0A5C0785658F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,7 +402,7 @@
     <t>10.2105/AJPH.2026.308569</t>
   </si>
   <si>
-    <t>https://doi.org/10.2105/AJPH.2026.308569</t>
+    <t>https://ajph.aphapublications.org/doi/10.2105/AJPH.2026.308569</t>
   </si>
 </sst>
 </file>
@@ -776,16 +776,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.7890625" customWidth="1"/>
-    <col min="4" max="4" width="65.26171875" customWidth="1"/>
-    <col min="5" max="5" width="34.47265625" customWidth="1"/>
-    <col min="6" max="6" width="42.47265625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.5234375" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="65.28515625" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -811,7 +811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -837,7 +837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -863,7 +863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -889,7 +889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -915,7 +915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -941,7 +941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -984,7 +984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1411,9 +1411,8 @@
     <hyperlink ref="F23" r:id="rId12" xr:uid="{414F80D1-F804-4ABF-AFEB-433C82EECD71}"/>
     <hyperlink ref="F24" r:id="rId13" xr:uid="{AF656063-5565-482A-8E9F-6EF001DB19F8}"/>
     <hyperlink ref="F25" r:id="rId14" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
-    <hyperlink ref="F26" r:id="rId15" xr:uid="{8821F420-E4C6-420E-A3D3-50FB15810E34}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BACAFB8E-14C7-4FE2-BD1C-AC3CD9F4041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D011DA-42D9-4FD3-9173-0A5C0785658F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B262B0A-9864-417E-A5A1-732202768911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="130">
   <si>
     <t>type</t>
   </si>
@@ -403,6 +403,18 @@
   </si>
   <si>
     <t>https://ajph.aphapublications.org/doi/10.2105/AJPH.2026.308569</t>
+  </si>
+  <si>
+    <t>Reciprocal relationships, reverse causality, and temporal ordering: Testing theories with cross-lagged panel models</t>
+  </si>
+  <si>
+    <t>Journal of Developmental and Life-Course Criminology</t>
+  </si>
+  <si>
+    <t>(Forthcoming)</t>
+  </si>
+  <si>
+    <t>CC Lanfear, TR Oliveira</t>
   </si>
 </sst>
 </file>
@@ -775,17 +787,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="65.28515625" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.83984375" customWidth="1"/>
+    <col min="4" max="4" width="65.26171875" customWidth="1"/>
+    <col min="5" max="5" width="34.41796875" customWidth="1"/>
+    <col min="6" max="6" width="42.41796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -811,7 +823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -837,7 +849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -863,7 +875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -889,7 +901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -915,7 +927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -941,7 +953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -967,7 +979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -984,7 +996,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1001,7 +1013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1018,7 +1030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1035,7 +1047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1055,7 +1067,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1078,7 +1090,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1104,7 +1116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1142,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1165,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1170,7 +1182,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1196,7 +1208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1234,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1245,7 +1257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1271,7 +1283,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1294,7 +1306,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +1332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1346,7 +1358,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1372,7 +1384,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1393,6 +1405,23 @@
       </c>
       <c r="G26" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cclan\OneDrive\GitHub\ccl_cv\cv_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B262B0A-9864-417E-A5A1-732202768911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6B262B0A-9864-417E-A5A1-732202768911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C048B95-A595-450E-AE92-5DBA44B229AE}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,9 +402,6 @@
     <t>10.2105/AJPH.2026.308569</t>
   </si>
   <si>
-    <t>https://ajph.aphapublications.org/doi/10.2105/AJPH.2026.308569</t>
-  </si>
-  <si>
     <t>Reciprocal relationships, reverse causality, and temporal ordering: Testing theories with cross-lagged panel models</t>
   </si>
   <si>
@@ -415,6 +412,9 @@
   </si>
   <si>
     <t>CC Lanfear, TR Oliveira</t>
+  </si>
+  <si>
+    <t>https://github.com/clanfear/ccl_cv/raw/master/articles/Lanfear (2026) place-based-interventions.pdf</t>
   </si>
 </sst>
 </file>
@@ -788,16 +788,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.83984375" customWidth="1"/>
-    <col min="4" max="4" width="65.26171875" customWidth="1"/>
-    <col min="5" max="5" width="34.41796875" customWidth="1"/>
-    <col min="6" max="6" width="42.41796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="65.28515625" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -823,7 +823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -849,7 +849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -875,7 +875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -901,7 +901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -927,7 +927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -953,7 +953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -996,7 +996,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1401,27 +1401,27 @@
         <v>123</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
         <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1436,12 +1436,13 @@
     <hyperlink ref="F15" r:id="rId8" xr:uid="{82618EFC-9AFF-4456-B2D7-390898DAEFAC}"/>
     <hyperlink ref="F21" r:id="rId9" xr:uid="{56FFA712-1D86-458E-843B-5469D57D0E50}"/>
     <hyperlink ref="F13" r:id="rId10" xr:uid="{01ED78A2-2779-4870-9D68-7C49B913842B}"/>
-    <hyperlink ref="F22" r:id="rId11" xr:uid="{BB7BBBBB-496F-4ADA-8F8E-0D25D142D88B}"/>
-    <hyperlink ref="F23" r:id="rId12" xr:uid="{414F80D1-F804-4ABF-AFEB-433C82EECD71}"/>
-    <hyperlink ref="F24" r:id="rId13" xr:uid="{AF656063-5565-482A-8E9F-6EF001DB19F8}"/>
-    <hyperlink ref="F25" r:id="rId14" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
+    <hyperlink ref="F23" r:id="rId11" xr:uid="{414F80D1-F804-4ABF-AFEB-433C82EECD71}"/>
+    <hyperlink ref="F24" r:id="rId12" xr:uid="{AF656063-5565-482A-8E9F-6EF001DB19F8}"/>
+    <hyperlink ref="F25" r:id="rId13" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
+    <hyperlink ref="F22" r:id="rId14" xr:uid="{BB7BBBBB-496F-4ADA-8F8E-0D25D142D88B}"/>
+    <hyperlink ref="F26" r:id="rId15" xr:uid="{B2F0E7D0-5303-4241-949D-31807ED13BC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6B262B0A-9864-417E-A5A1-732202768911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C048B95-A595-450E-AE92-5DBA44B229AE}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D865A6-D6F1-4305-85FD-80E3C774BC42}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-11745" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-3720" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
   <si>
     <t>type</t>
   </si>
@@ -408,20 +408,26 @@
     <t>Journal of Developmental and Life-Course Criminology</t>
   </si>
   <si>
-    <t>(Forthcoming)</t>
-  </si>
-  <si>
     <t>CC Lanfear, TR Oliveira</t>
   </si>
   <si>
     <t>https://github.com/clanfear/ccl_cv/raw/master/articles/Lanfear (2026) place-based-interventions.pdf</t>
+  </si>
+  <si>
+    <t>10.1007/s40865-026-00314-y</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s40865-026-00314-y</t>
+  </si>
+  <si>
+    <t>12(24)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +449,11 @@
       <color rgb="FF000000"/>
       <name val="Book Antiqua"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <color rgb="FF222222"/>
+      <name val="Merriweather Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -466,12 +477,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1401,7 +1413,7 @@
         <v>123</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G26" t="s">
         <v>124</v>
@@ -1412,16 +1424,25 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" t="s">
         <v>127</v>
+      </c>
+      <c r="C27">
+        <v>2026</v>
       </c>
       <c r="D27" t="s">
         <v>125</v>
       </c>
       <c r="E27" t="s">
         <v>126</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1441,8 +1462,9 @@
     <hyperlink ref="F25" r:id="rId13" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
     <hyperlink ref="F22" r:id="rId14" xr:uid="{BB7BBBBB-496F-4ADA-8F8E-0D25D142D88B}"/>
     <hyperlink ref="F26" r:id="rId15" xr:uid="{B2F0E7D0-5303-4241-949D-31807ED13BC1}"/>
+    <hyperlink ref="F27" r:id="rId16" xr:uid="{603E4735-1CCF-4E70-BD58-F04E8CCFF17D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D865A6-D6F1-4305-85FD-80E3C774BC42}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C147D2B-EF72-4132-BDE5-C3DCB7D82D3D}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-3720" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
   <si>
     <t>type</t>
   </si>
@@ -370,9 +370,6 @@
   </si>
   <si>
     <t>https://doi.org/10.1007/s10940-025-09616-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>C Engel, CC Lanfear, DS Nagin</t>
@@ -500,6 +497,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1349,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24">
         <v>2025</v>
@@ -1366,8 +1367,8 @@
       <c r="G24" t="s">
         <v>113</v>
       </c>
-      <c r="H24" t="s">
-        <v>115</v>
+      <c r="H24">
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,25 +1376,25 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25">
         <v>2025</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
       </c>
       <c r="F25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" t="s">
         <v>119</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>120</v>
-      </c>
-      <c r="H25" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1407,16 +1408,16 @@
         <v>2026</v>
       </c>
       <c r="D26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="s">
         <v>122</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" t="s">
         <v>123</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1424,25 +1425,25 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27">
         <v>2026</v>
       </c>
       <c r="D27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" t="s">
         <v>125</v>
       </c>
-      <c r="E27" t="s">
-        <v>126</v>
-      </c>
       <c r="F27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" t="s">
         <v>130</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H27" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C147D2B-EF72-4132-BDE5-C3DCB7D82D3D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FA43C1-EB05-447E-A3AC-B4EDF6735968}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
   <si>
     <t>type</t>
   </si>
@@ -408,9 +408,6 @@
     <t>CC Lanfear, TR Oliveira</t>
   </si>
   <si>
-    <t>https://github.com/clanfear/ccl_cv/raw/master/articles/Lanfear (2026) place-based-interventions.pdf</t>
-  </si>
-  <si>
     <t>10.1007/s40865-026-00314-y</t>
   </si>
   <si>
@@ -418,6 +415,12 @@
   </si>
   <si>
     <t>12(24)</t>
+  </si>
+  <si>
+    <t>116(8)</t>
+  </si>
+  <si>
+    <t>https://ajph.aphapublications.org/doi/10.2105/AJPH.2026.308569</t>
   </si>
 </sst>
 </file>
@@ -1413,12 +1416,15 @@
       <c r="E26" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>127</v>
+      <c r="F26" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="G26" t="s">
         <v>123</v>
       </c>
+      <c r="H26" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1437,13 +1443,13 @@
         <v>125</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" t="s">
         <v>129</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1462,10 +1468,9 @@
     <hyperlink ref="F24" r:id="rId12" xr:uid="{AF656063-5565-482A-8E9F-6EF001DB19F8}"/>
     <hyperlink ref="F25" r:id="rId13" xr:uid="{3659F2BA-3C68-4FBE-8D5E-141D76D2601C}"/>
     <hyperlink ref="F22" r:id="rId14" xr:uid="{BB7BBBBB-496F-4ADA-8F8E-0D25D142D88B}"/>
-    <hyperlink ref="F26" r:id="rId15" xr:uid="{B2F0E7D0-5303-4241-949D-31807ED13BC1}"/>
-    <hyperlink ref="F27" r:id="rId16" xr:uid="{603E4735-1CCF-4E70-BD58-F04E8CCFF17D}"/>
+    <hyperlink ref="F27" r:id="rId15" xr:uid="{603E4735-1CCF-4E70-BD58-F04E8CCFF17D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>